--- a/TLCN_EDA_AQI/EDA_AQI/Jobs/src/eda/eda_reports/openmeteo_2024_eda_report.xlsx
+++ b/TLCN_EDA_AQI/EDA_AQI/Jobs/src/eda/eda_reports/openmeteo_2024_eda_report.xlsx
@@ -697,10 +697,10 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>379.0556175209241</v>
+        <v>379.0558869982246</v>
       </c>
       <c r="G8" t="n">
-        <v>246.8572112033226</v>
+        <v>246.857373798771</v>
       </c>
       <c r="H8" t="n">
         <v>80</v>

--- a/TLCN_EDA_AQI/EDA_AQI/Jobs/src/eda/eda_reports/openmeteo_2024_eda_report.xlsx
+++ b/TLCN_EDA_AQI/EDA_AQI/Jobs/src/eda/eda_reports/openmeteo_2024_eda_report.xlsx
@@ -527,10 +527,10 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>21.85531749325586</v>
+        <v>21.99495616310438</v>
       </c>
       <c r="G3" t="n">
-        <v>16.48978716020579</v>
+        <v>16.64457087317276</v>
       </c>
       <c r="H3" t="n">
         <v>0.1</v>
@@ -542,7 +542,7 @@
         <v>17.2</v>
       </c>
       <c r="K3" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="L3" t="n">
         <v>206.3</v>
@@ -561,22 +561,22 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>31.19943006271471</v>
+        <v>31.38687559083259</v>
       </c>
       <c r="G4" t="n">
-        <v>21.65019987161173</v>
+        <v>21.85861056227843</v>
       </c>
       <c r="H4" t="n">
         <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="J4" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="K4" t="n">
-        <v>39.2</v>
+        <v>39.5</v>
       </c>
       <c r="L4" t="n">
         <v>210.9</v>
@@ -595,10 +595,10 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>10.79754112771207</v>
+        <v>10.64037086993613</v>
       </c>
       <c r="G5" t="n">
-        <v>12.06633540560605</v>
+        <v>11.81681909935397</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -607,10 +607,10 @@
         <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="K5" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="L5" t="n">
         <v>111.5</v>
@@ -629,10 +629,10 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>72.07482966728921</v>
+        <v>72.38332497521385</v>
       </c>
       <c r="G6" t="n">
-        <v>40.17834500655702</v>
+        <v>40.21184521456673</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -641,10 +641,10 @@
         <v>44</v>
       </c>
       <c r="J6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K6" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L6" t="n">
         <v>383</v>
@@ -663,10 +663,10 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>13.26332846256715</v>
+        <v>13.25154927831961</v>
       </c>
       <c r="G7" t="n">
-        <v>13.19875808675575</v>
+        <v>13.18308485054303</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -675,7 +675,7 @@
         <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>19.7</v>
@@ -697,10 +697,10 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>379.0558869982246</v>
+        <v>379.8920635332365</v>
       </c>
       <c r="G8" t="n">
-        <v>246.857373798771</v>
+        <v>247.6177226135961</v>
       </c>
       <c r="H8" t="n">
         <v>80</v>
@@ -709,10 +709,10 @@
         <v>224</v>
       </c>
       <c r="J8" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K8" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L8" t="n">
         <v>5190</v>
@@ -731,10 +731,10 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>0.4191760335247054</v>
+        <v>0.4222925745313689</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3324832718932262</v>
+        <v>0.3355524685455415</v>
       </c>
       <c r="H9" t="n">
         <v>0.01</v>
@@ -765,10 +765,10 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.3442939982937908</v>
+        <v>0.3407864702220378</v>
       </c>
       <c r="G10" t="n">
-        <v>1.191388546409</v>
+        <v>1.184296030264689</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>1.650245843997141</v>
+        <v>1.641453462567153</v>
       </c>
       <c r="G11" t="n">
-        <v>2.796292409300824</v>
+        <v>2.785368433441421</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>71.96768578082128</v>
+        <v>72.28990569735538</v>
       </c>
       <c r="G12" t="n">
-        <v>34.34258518818933</v>
+        <v>34.61841025761927</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -845,10 +845,10 @@
         <v>50</v>
       </c>
       <c r="J12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L12" t="n">
         <v>272</v>
@@ -867,10 +867,10 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>68.93833869405825</v>
+        <v>69.22804264370201</v>
       </c>
       <c r="G13" t="n">
-        <v>31.29004362178947</v>
+        <v>31.55439256852129</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -879,10 +879,10 @@
         <v>50</v>
       </c>
       <c r="J13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K13" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L13" t="n">
         <v>192</v>
@@ -901,10 +901,10 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>27.55596049203385</v>
+        <v>27.69564916649374</v>
       </c>
       <c r="G14" t="n">
-        <v>14.9972282012389</v>
+        <v>15.11599746006521</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -935,10 +935,10 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>5.313951142468469</v>
+        <v>5.236531899195315</v>
       </c>
       <c r="G15" t="n">
-        <v>5.954604773973044</v>
+        <v>5.831836602003152</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -969,10 +969,10 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>38.01082088261742</v>
+        <v>38.23570185146757</v>
       </c>
       <c r="G16" t="n">
-        <v>29.90006010975904</v>
+        <v>30.09069456956808</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1003,10 +1003,10 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>7.236057792073044</v>
+        <v>7.22966238961518</v>
       </c>
       <c r="G17" t="n">
-        <v>7.199459604214665</v>
+        <v>7.190964614010873</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1037,10 +1037,10 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3.663092850061101</v>
+        <v>3.671293894537825</v>
       </c>
       <c r="G18" t="n">
-        <v>2.207747239170527</v>
+        <v>2.215797337933267</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>hanoi_hoankiem</t>
+          <t>yenbai_yenbaicity</t>
         </is>
       </c>
       <c r="E19" t="n">
